--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536305_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536305_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,67 +807,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2918</v>
+        <v>-0.4769</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2918</v>
+        <v>-1.1115</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2918</v>
+        <v>-0.5016</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2918</v>
+        <v>0.0332</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.5347</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2918</v>
+        <v>0.7768</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2918</v>
+        <v>1.0902</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.3133</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.2784</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.057</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.2214</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.411</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.4658</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.5521</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.5158</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.0363</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.9384</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3493</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.589</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>D. LOZANO GIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4769</v>
+        <v>-1.1466</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1115</v>
+        <v>-1.1545</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5016</v>
+        <v>-0.1052</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0332</v>
+        <v>-0.389</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5347</v>
+        <v>0.2838</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7768</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0902</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3133</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2784</v>
+        <v>-0.1052</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.057</v>
+        <v>-0.389</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2214</v>
+        <v>0.2838</v>
       </c>
       <c r="P6" t="n">
-        <v>0.411</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0548</v>
+        <v>-1.0274</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4658</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5521</v>
+        <v>-0.3633</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5158</v>
+        <v>-0.1271</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0363</v>
+        <v>-0.2361</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9384</v>
+        <v>0.3493</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3493</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.589</v>
+        <v>0.3493</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. LOZANO GIMENEZ</t>
+          <t>G. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1466</v>
+        <v>-1.3494</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1545</v>
+        <v>-0.19</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008</v>
+        <v>-1.1594</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1052</v>
+        <v>-1.3928</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.389</v>
+        <v>-0.8351</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2838</v>
+        <v>-0.5577</v>
       </c>
       <c r="J7" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.2038</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1.3891</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.6313</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.7578</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2603</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-0.1052</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.389</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.2838</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-1.0274</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-1.0274</v>
-      </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.2603</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3633</v>
+        <v>-0.4498</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1271</v>
+        <v>-0.1863</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2361</v>
+        <v>-0.2635</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3493</v>
+        <v>-1.7671</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3493</v>
+        <v>-1.7671</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. IGLESIAS FERNANDEZ</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3494</v>
+        <v>-1.9367</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.19</v>
+        <v>-3.4612</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1594</v>
+        <v>1.5245</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3928</v>
+        <v>-3.4736</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8351</v>
+        <v>-0.706</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5577</v>
+        <v>-2.7676</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0037</v>
+        <v>-3.3519</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2038</v>
+        <v>0.1565</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2001</v>
+        <v>-3.5084</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3891</v>
+        <v>-0.1217</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6313</v>
+        <v>-0.8625</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7578</v>
+        <v>0.7408</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2603</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2603</v>
+        <v>1.6439</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4498</v>
+        <v>0.0917</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1863</v>
+        <v>-0.4997</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2635</v>
+        <v>0.5914</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7671</v>
+        <v>0.8288</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7671</v>
+        <v>-0.589</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9367</v>
+        <v>-3.3173</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4612</v>
+        <v>-3.3873</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5245</v>
+        <v>0.0699</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4736</v>
+        <v>-3.9429</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.706</v>
+        <v>-4.1013</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7676</v>
+        <v>0.1584</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.3519</v>
+        <v>-2.2075</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1565</v>
+        <v>-2.0509</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.5084</v>
+        <v>-0.1567</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1217</v>
+        <v>-1.7354</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8625</v>
+        <v>-2.0504</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7408</v>
+        <v>0.315</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0274</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6439</v>
+        <v>1.4384</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0917</v>
+        <v>-0.2443</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4997</v>
+        <v>-0.1523</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5914</v>
+        <v>-0.092</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8288</v>
+        <v>0.4589</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4178</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.589</v>
+        <v>0.4589</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>K. BAOKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3173</v>
+        <v>-3.4185</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3873</v>
+        <v>-2.9156</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0699</v>
+        <v>-0.5029</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9429</v>
+        <v>-2.1199</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.1013</v>
+        <v>-1.6618</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1584</v>
+        <v>-0.4581</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2075</v>
+        <v>-0.5889</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.0509</v>
+        <v>-0.7467</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1567</v>
+        <v>0.1578</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7354</v>
+        <v>-1.531</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.0504</v>
+        <v>-0.9151</v>
       </c>
       <c r="O10" t="n">
-        <v>0.315</v>
+        <v>-0.6159</v>
       </c>
       <c r="P10" t="n">
-        <v>0.411</v>
+        <v>-1.4384</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0274</v>
+        <v>-3.0822</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4384</v>
+        <v>1.6439</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2443</v>
+        <v>0.3795</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1523</v>
+        <v>0.5158</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.092</v>
+        <v>-0.1363</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4589</v>
+        <v>-0.2397</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4589</v>
+        <v>-0.4794</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. BAOKO</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4185</v>
+        <v>-3.7236</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9156</v>
+        <v>-5.3938</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5029</v>
+        <v>1.6702</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1199</v>
+        <v>-1.8778</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6618</v>
+        <v>-1.6959</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4581</v>
+        <v>-0.1819</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5889</v>
+        <v>-1.6613</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7467</v>
+        <v>-1.7007</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1578</v>
+        <v>0.0395</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.531</v>
+        <v>-0.2165</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9151</v>
+        <v>0.0049</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6159</v>
+        <v>-0.2214</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4384</v>
+        <v>-2.4658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0822</v>
+        <v>-4.1096</v>
       </c>
       <c r="R11" t="n">
         <v>1.6439</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3795</v>
+        <v>0.3803</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5158</v>
+        <v>0.1374</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1363</v>
+        <v>0.2429</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2397</v>
+        <v>0.2397</v>
       </c>
       <c r="W11" t="n">
         <v>0.2397</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4794</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. DIAZ DEL VALLE</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0153</v>
+        <v>-6.4296</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6855</v>
+        <v>-3.479</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6702</v>
+        <v>-2.9506</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1696</v>
+        <v>-1.4586</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9876</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1819</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9531</v>
+        <v>0.2242</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9925</v>
+        <v>0.9726</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0395</v>
+        <v>-0.7484</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2165</v>
+        <v>-1.6827</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0049</v>
+        <v>-1.714</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2214</v>
+        <v>0.0312</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4658</v>
+        <v>-1.6439</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.1096</v>
+        <v>-3.0822</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6439</v>
+        <v>1.4384</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3803</v>
+        <v>-0.4915</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1374</v>
+        <v>-0.6209</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2429</v>
+        <v>0.1294</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2397</v>
+        <v>-2.8356</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.8356</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,157 +1471,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4296</v>
+        <v>-7.598600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.479</v>
+        <v>-15.2502</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9506</v>
+        <v>7.6517</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4586</v>
+        <v>-12.9804</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-9.1203</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-3.86</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2242</v>
+        <v>-4.0071</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9726</v>
+        <v>-0.2322000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7484</v>
+        <v>-3.7748</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6827</v>
+        <v>-8.973099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.714</v>
+        <v>-8.8879</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0312</v>
+        <v>-0.0852999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.6439</v>
+        <v>4.109600000000002</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0822</v>
+        <v>-16.4384</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4384</v>
+        <v>20.5484</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4915</v>
+        <v>3.0599</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6209</v>
+        <v>2.209300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1294</v>
+        <v>0.8507</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.8356</v>
+        <v>-1.7877</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.9862</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.8356</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536305_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-4.7738</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. MEDOR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMICS CASTELLÓ</t>
+          <t>C.B. ZARAGOZA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.598499999999999</v>
+        <v>6.9449</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.2501</v>
+        <v>5.2423</v>
       </c>
       <c r="F14" t="n">
-        <v>7.6517</v>
+        <v>1.7026</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.9804</v>
+        <v>2.3631</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.120200000000001</v>
+        <v>-0.0588</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.86</v>
+        <v>2.4219</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.0071</v>
+        <v>1.6602</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2322000000000001</v>
+        <v>0.0415</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.7748</v>
+        <v>1.6187</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.973100000000001</v>
+        <v>0.7029</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.8879</v>
+        <v>-0.1003</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0852999999999999</v>
+        <v>0.8032</v>
       </c>
       <c r="P14" t="n">
-        <v>4.1096</v>
+        <v>1.6439</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.4384</v>
+        <v>-0.2055</v>
       </c>
       <c r="R14" t="n">
-        <v>20.5484</v>
+        <v>1.8493</v>
       </c>
       <c r="S14" t="n">
-        <v>3.059900000000001</v>
+        <v>-0.7059</v>
       </c>
       <c r="T14" t="n">
-        <v>2.209300000000001</v>
+        <v>-0.3356</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8507</v>
+        <v>-0.3702</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7877</v>
+        <v>3.6438</v>
       </c>
       <c r="W14" t="n">
-        <v>2.9862</v>
+        <v>4.1233</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.7738</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+        <v>-0.4794</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2536305_LIGAREGULARB_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MEDOR</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9449</v>
+        <v>3.6365</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2423</v>
+        <v>1.1671</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7026</v>
+        <v>2.4694</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3631</v>
+        <v>2.6884</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0588</v>
+        <v>2.2715</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4219</v>
+        <v>0.4169</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6602</v>
+        <v>2.5005</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0415</v>
+        <v>2.4611</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6187</v>
+        <v>0.0395</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7029</v>
+        <v>0.1879</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1003</v>
+        <v>-0.1896</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8032</v>
+        <v>0.3775</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6439</v>
+        <v>1.0274</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2055</v>
+        <v>-1.2329</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8493</v>
+        <v>2.2603</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7059</v>
+        <v>0.0303</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3356</v>
+        <v>-0.2307</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3702</v>
+        <v>0.261</v>
       </c>
       <c r="V15" t="n">
-        <v>3.6438</v>
+        <v>-0.1096</v>
       </c>
       <c r="W15" t="n">
-        <v>4.1233</v>
+        <v>0.1301</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4794</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6365</v>
+        <v>3.5549</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1671</v>
+        <v>1.933</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4694</v>
+        <v>1.622</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6884</v>
+        <v>0.7589</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2715</v>
+        <v>-0.4553</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4169</v>
+        <v>1.2142</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5005</v>
+        <v>0.6603</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4611</v>
+        <v>-0.6021</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>1.2625</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1879</v>
+        <v>0.0985</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1896</v>
+        <v>0.1468</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3775</v>
+        <v>-0.0483</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0274</v>
+        <v>1.4384</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2329</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2603</v>
+        <v>1.4384</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0303</v>
+        <v>0.1796</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2307</v>
+        <v>0.0946</v>
       </c>
       <c r="U16" t="n">
-        <v>0.261</v>
+        <v>0.0851</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1096</v>
+        <v>1.1781</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1301</v>
+        <v>1.1781</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2397</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>A. YOUNG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,64 +1799,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5549</v>
+        <v>2.8127</v>
       </c>
       <c r="E17" t="n">
-        <v>1.933</v>
+        <v>1.3298</v>
       </c>
       <c r="F17" t="n">
-        <v>1.622</v>
+        <v>1.4828</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7589</v>
+        <v>0.9744</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4553</v>
+        <v>1.4408</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2142</v>
+        <v>-0.4663</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6603</v>
+        <v>1.2863</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6021</v>
+        <v>1.8775</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2625</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0985</v>
+        <v>-0.3119</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1468</v>
+        <v>-0.4368</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0483</v>
+        <v>0.1249</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4384</v>
+        <v>1.2329</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.2055</v>
       </c>
       <c r="R17" t="n">
         <v>1.4384</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1796</v>
+        <v>-0.1138</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0946</v>
+        <v>-0.4702</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0851</v>
+        <v>0.3563</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1781</v>
+        <v>0.7192</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1781</v>
+        <v>0.7192</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. YOUNG</t>
+          <t>D. MUNOZ SAMATAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8127</v>
+        <v>2.5452</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3298</v>
+        <v>-0.0445</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4828</v>
+        <v>2.5897</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9744</v>
+        <v>1.8048</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4408</v>
+        <v>1.1353</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4663</v>
+        <v>0.6695</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2863</v>
+        <v>0.6915</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8775</v>
+        <v>0.6521</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0.0395</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3119</v>
+        <v>1.1133</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4368</v>
+        <v>0.4832</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1249</v>
+        <v>0.6301</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2329</v>
+        <v>0.8219</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2055</v>
+        <v>-1.0274</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4384</v>
+        <v>1.8493</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1138</v>
+        <v>-0.4309</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4702</v>
+        <v>0.0517</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3563</v>
+        <v>-0.4826</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7192</v>
+        <v>0.3493</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7192</v>
+        <v>0.2397</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.1096</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MUNOZ SAMATAN</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5452</v>
+        <v>1.3692</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0445</v>
+        <v>-2.1128</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5897</v>
+        <v>3.482</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8048</v>
+        <v>0.6484</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1353</v>
+        <v>1.2397</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6695</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6915</v>
+        <v>0.5615</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6521</v>
+        <v>0.9142</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0395</v>
+        <v>-0.3528</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1133</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4832</v>
+        <v>0.3254</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6301</v>
+        <v>-0.2384</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8219</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0274</v>
+        <v>-2.0548</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8493</v>
+        <v>2.6713</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4309</v>
+        <v>-0.245</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0517</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4826</v>
+        <v>0.3745</v>
       </c>
       <c r="V19" t="n">
         <v>0.3493</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1096</v>
+        <v>0.3493</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3692</v>
+        <v>-1.4094</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1128</v>
+        <v>-3.1701</v>
       </c>
       <c r="F20" t="n">
-        <v>3.482</v>
+        <v>1.7607</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6484</v>
+        <v>-0.4131</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2397</v>
+        <v>-0.1994</v>
       </c>
       <c r="I20" t="n">
+        <v>-0.2137</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.4355</v>
+      </c>
+      <c r="L20" t="n">
         <v>-0.5911999999999999</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.5615</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.9142</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-0.3528</v>
-      </c>
       <c r="M20" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.6136</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3254</v>
+        <v>0.2361</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2384</v>
+        <v>0.3775</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6163999999999999</v>
+        <v>-2.0548</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0548</v>
+        <v>-3.0822</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6713</v>
+        <v>1.0274</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.245</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6195000000000001</v>
+        <v>0.6992</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3745</v>
+        <v>0.0101</v>
       </c>
       <c r="V20" t="n">
         <v>0.3493</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3493</v>
+        <v>0.1096</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4094</v>
+        <v>-2.9194</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1701</v>
+        <v>-6.1313</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7607</v>
+        <v>3.2119</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4131</v>
+        <v>3.2687</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1994</v>
+        <v>2.7087</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2137</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0267</v>
+        <v>2.0239</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4355</v>
+        <v>2.7723</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.7484</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6136</v>
+        <v>1.2448</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2361</v>
+        <v>-0.0636</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3775</v>
+        <v>1.3084</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0548</v>
+        <v>-5.3425</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0822</v>
+        <v>-7.3973</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0274</v>
+        <v>2.0548</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6992</v>
+        <v>-0.0592</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0101</v>
+        <v>0.152</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3493</v>
+        <v>-0.9384</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2397</v>
+        <v>-0.6986</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1096</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9194</v>
+        <v>-6.8813</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.1313</v>
+        <v>-5.8653</v>
       </c>
       <c r="F22" t="n">
-        <v>3.2119</v>
+        <v>-1.016</v>
       </c>
       <c r="G22" t="n">
-        <v>3.2687</v>
+        <v>0.8868</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7087</v>
+        <v>1.038</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.1513</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0239</v>
+        <v>0.6157</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7723</v>
+        <v>1.2069</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7484</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2448</v>
+        <v>0.2711</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0636</v>
+        <v>-0.1688</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3084</v>
+        <v>0.4399</v>
       </c>
       <c r="P22" t="n">
+        <v>-3.4932</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-5.3425</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-7.3973</v>
-      </c>
       <c r="R22" t="n">
-        <v>2.0548</v>
+        <v>1.8493</v>
       </c>
       <c r="S22" t="n">
-        <v>0.09279999999999999</v>
+        <v>-0.5214</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0592</v>
+        <v>0.0191</v>
       </c>
       <c r="U22" t="n">
-        <v>0.152</v>
+        <v>-0.5406</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9384</v>
+        <v>-3.7534</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6986</v>
+        <v>-1.1576</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2397</v>
+        <v>-2.5959</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,152 +2297,69 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8813</v>
+        <v>9.653299999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.8653</v>
+        <v>-7.651800000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.016</v>
+        <v>17.3051</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8868</v>
+        <v>12.9804</v>
       </c>
       <c r="H23" t="n">
-        <v>1.038</v>
+        <v>9.1205</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1513</v>
+        <v>3.86</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6157</v>
+        <v>8.9732</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2069</v>
+        <v>8.888000000000002</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0.08540000000000059</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2711</v>
+        <v>4.0072</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1688</v>
+        <v>0.2323999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4399</v>
+        <v>3.7748</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.4932</v>
+        <v>-4.1096</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.3425</v>
+        <v>-20.5481</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8493</v>
+        <v>16.4385</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5214</v>
+        <v>-1.0051</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0191</v>
+        <v>-0.8506</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5406</v>
+        <v>-0.1543999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.7534</v>
+        <v>1.787599999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.1576</v>
+        <v>4.773900000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.5959</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>play_by_play_2536305_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>C.B. ZARAGOZA</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9.653299999999998</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-7.651800000000001</v>
-      </c>
-      <c r="F24" t="n">
-        <v>17.3051</v>
-      </c>
-      <c r="G24" t="n">
-        <v>12.9804</v>
-      </c>
-      <c r="H24" t="n">
-        <v>9.1205</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="J24" t="n">
-        <v>8.9732</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8.888000000000002</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.08540000000000059</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.0072</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.2323999999999999</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.7748</v>
-      </c>
-      <c r="P24" t="n">
-        <v>-4.1096</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-20.5481</v>
-      </c>
-      <c r="R24" t="n">
-        <v>16.4385</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-1.0051</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-0.8506</v>
-      </c>
-      <c r="U24" t="n">
-        <v>-0.1543999999999999</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.787599999999999</v>
-      </c>
-      <c r="W24" t="n">
-        <v>4.773900000000001</v>
-      </c>
-      <c r="X24" t="n">
         <v>-2.9862</v>
       </c>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
